--- a/stories/arbres/ATOM-LAN.SON.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zoé marche à la ferme avec papa. Un son arrive : meuh. Papa dit : c'est un son. Quel nom ? Zoé dit : la vache. Un autre son : cot cot. Zoé dit le nom : la poule. Près de l'auge, l'eau cloche. Zoé dit : l'eau. Papa dit : on entend un son. On dit le nom. Zoé répète : son, nom. La vache, la poule, l'eau.</t>
+          <t>Zoé marche à la ferme avec papa. Un son arrive : meuh. C'est un son. Quel nom ? La vache. Un autre son : cot cot. Zoé dit le nom : la poule. Près de l'auge, l'eau cloche. L'eau. On entend un son. On dit le nom. Zoé répète : son, nom. La vache, la poule, l'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé marche à la ferme avec papa. Un son arrive : meuh.
+papa|C'est un son. Quel nom ?
+enfant-f|La vache.
+narrateur|Un autre son : cot cot. Zoé dit le nom : la poule. Près de l'auge, l'eau cloche.
+enfant-f|L'eau.
+papa|On entend un son. On dit le nom.
+narrateur|Zoé répète : son, nom. La vache, la poule, l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé entend un bruit. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a entendu un son. Elle a dit le nom. Vache. Poule. Eau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa donne la main. Zoé écoute encore l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Zoé répète : son, nom. La vache, la poule, l'eau.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Zoé entend un bruit. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Zoé a entendu un son. Elle a dit le nom. Vache. Poule. Eau.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Papa donne la main. Zoé écoute encore l'eau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.SON.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zoé nomme les sons de la ferme</t>
+          <t>La paille et les sons de Victorina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La paille sent le soleil. Victorina marche avec papa. Elle entend la vache, la poule, l'eau. Elle dit le nom de chaque son.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zoé marche à la ferme avec papa. Un son arrive : meuh. C'est un son. Quel nom ? La vache. Un autre son : cot cot. Zoé dit le nom : la poule. Près de l'auge, l'eau cloche. L'eau. On entend un son. On dit le nom. Zoé répète : son, nom. La vache, la poule, l'eau.</t>
+          <t>La paille sent le soleil. Un grain de poussière danse dans un rayon. La barrière de bois est chaude. La terre est un peu collante sous les bottes. Un seau métallique attend près de l'auge. Une plume blanche est coincée dans le grillage. Le coq s'est tu, plus loin. La ferme est calme, ce matin, Victorina. Tu sens la paille ? Oui, papa. Ça pique un peu. J'arrive avec le panier. Je vous rejoins. En ce moment, Victorina marche près de papa. Un son arrive, grave. Meuh. C'est un son. Quel nom ? La vache. Oui. Le nom du son, c'est la vache. Un autre son, plus vif. Cot cot. Encore un son. Quel nom ? La poule. Oui. Le nom du son, c'est la poule. Près de l'auge, l'eau cloche. Un son. Quel nom ? L'eau. Oui. On entend un son. On dit le nom. Victorina répète, tout bas. Son. Nom. La vache, la poule, l'eau. Tu as nommé le son. Bravo, Victorina. Maman pose le panier. Dedans, des œufs. On compte des objets ? Un. Deux. Trois. Trois œufs. Tu as dit le nombre. Et tu as nommé les sons. C'est du bon travail. Tu as fini d'écouter l'eau ? Encore un peu. D'accord.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,60 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Zoé marche à la ferme avec papa. Un son arrive : meuh.
-papa|C'est un son. Quel nom ?
+          <t>narrateur|La paille sent le soleil.
+narrateur|Un grain de poussière danse dans un rayon.
+narrateur|La barrière de bois est chaude.
+narrateur|La terre est un peu collante sous les bottes.
+narrateur|Un seau métallique attend près de l'auge.
+narrateur|Une plume blanche est coincée dans le grillage.
+narrateur|Le coq s'est tu, plus loin.
+papa|La ferme est calme, ce matin, Victorina.
+papa|Tu sens la paille ?
+enfant-f|Oui, papa.
+enfant-f|Ça pique un peu.
+maman|J'arrive avec le panier.
+maman|Je vous rejoins.
+narrateur|En ce moment, Victorina marche près de papa.
+narrateur|Un son arrive, grave.
+narrateur|Meuh.
+papa|C'est un son.
+papa|Quel nom ?
 enfant-f|La vache.
-narrateur|Un autre son : cot cot. Zoé dit le nom : la poule. Près de l'auge, l'eau cloche.
+papa|Oui.
+papa|Le nom du son, c'est la vache.
+narrateur|Un autre son, plus vif.
+narrateur|Cot cot.
+papa|Encore un son.
+papa|Quel nom ?
+enfant-f|La poule.
+papa|Oui.
+papa|Le nom du son, c'est la poule.
+narrateur|Près de l'auge, l'eau cloche.
+papa|Un son.
+papa|Quel nom ?
 enfant-f|L'eau.
-papa|On entend un son. On dit le nom.
-narrateur|Zoé répète : son, nom. La vache, la poule, l'eau.</t>
+papa|Oui.
+papa|On entend un son.
+papa|On dit le nom.
+narrateur|Victorina répète, tout bas.
+enfant-f|Son.
+enfant-f|Nom.
+enfant-f|La vache, la poule, l'eau.
+maman|Tu as nommé le son.
+maman|Bravo, Victorina.
+narrateur|Maman pose le panier.
+narrateur|Dedans, des œufs.
+maman|On compte des objets ?
+enfant-f|Un.
+enfant-f|Deux.
+enfant-f|Trois.
+enfant-f|Trois œufs.
+papa|Tu as dit le nombre.
+papa|Et tu as nommé les sons.
+papa|C'est du bon travail.
+papa|Tu as fini d'écouter l'eau ?
+enfant-f|Encore un peu.
+maman|D'accord.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1346,7 +1405,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Zoé entend un bruit. C'est quoi ?</t>
+          <t>Victorina entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1561,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Zoé entend un bruit. C'est quoi ?</t>
+          <t>narrateur|Victorina entend un bruit.
+narrateur|C'est quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Zoé a entendu un son. Elle a dit le nom. Vache. Poule. Eau.</t>
+          <t>Victorina a entendu un son. Elle a dit le nom. Vache. Poule. Eau. Bravo. Tu as nommé le son. C'est du bon travail, Victorina. L'eau cloche encore. Oui. On dit le nom.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1734,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a entendu un son. Elle a dit le nom. Vache. Poule. Eau.</t>
+          <t>narrateur|Victorina a entendu un son.
+narrateur|Elle a dit le nom.
+papa|Vache.
+papa|Poule.
+papa|Eau.
+papa|Bravo.
+maman|Tu as nommé le son.
+maman|C'est du bon travail, Victorina.
+enfant-f|L'eau cloche encore.
+papa|Oui.
+papa|On dit le nom.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1772,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa donne la main. Zoé écoute encore l'eau.</t>
+          <t>Papa donne la main. La main est chaude, un peu rêche. On écoute encore l'eau ? Oui, papa. Victorina écoute l'auge. L'eau cloche, tout doucement. Le panier est prêt. On rentre après, d'accord ? D'accord, maman. Tu as nommé le son.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1912,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa donne la main. Zoé écoute encore l'eau.</t>
+          <t>narrateur|Papa donne la main.
+narrateur|La main est chaude, un peu rêche.
+papa|On écoute encore l'eau ?
+enfant-f|Oui, papa.
+narrateur|Victorina écoute l'auge.
+narrateur|L'eau cloche, tout doucement.
+maman|Le panier est prêt.
+maman|On rentre après, d'accord ?
+enfant-f|D'accord, maman.
+papa|Tu as nommé le son.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1949,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Victorina. Tu as fait du bon travail. La paille reste chaude dans le rayon. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2089,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai entendu un son.
+enfant-f|J'ai dit le nom.
+papa|Bravo, Victorina.
+maman|Tu as fait du bon travail.
+narrateur|La paille reste chaude dans le rayon.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La paille sent le soleil. Un grain de poussière danse dans un rayon. La barrière de bois est chaude. La terre est un peu collante sous les bottes. Un seau métallique attend près de l'auge. Une plume blanche est coincée dans le grillage. Le coq s'est tu, plus loin. La ferme est calme, ce matin, Victorina. Tu sens la paille ? Oui, papa. Ça pique un peu. J'arrive avec le panier. Je vous rejoins. En ce moment, Victorina marche près de papa. Un son arrive, grave. Meuh. C'est un son. Quel nom ? La vache. Oui. Le nom du son, c'est la vache. Un autre son, plus vif. Cot cot. Encore un son. Quel nom ? La poule. Oui. Le nom du son, c'est la poule. Près de l'auge, l'eau cloche. Un son. Quel nom ? L'eau. Oui. On entend un son. On dit le nom. Victorina répète, tout bas. Son. Nom. La vache, la poule, l'eau. Tu as nommé le son. Bravo, Victorina. Maman pose le panier. Dedans, des œufs. On compte des objets ? Un. Deux. Trois. Trois œufs. Tu as dit le nombre. Et tu as nommé les sons. C'est du bon travail. Tu as fini d'écouter l'eau ? Encore un peu. D'accord.</t>
+          <t>La paille sent le soleil. Un grain de poussière danse dans un rayon. La barrière de bois est chaude. La terre est un peu collante sous les bottes. Un seau métallique attend près de l'auge. Une plume blanche est coincée dans le grillage. Le coq s'est tu, plus loin. La ferme est calme, ce matin, Victorina. Tu sens la paille ? Oui, papa. Ça pique un peu. J'arrive avec le panier. Je vous rejoins. En ce moment, Victorina marche près de papa. Un son arrive, grave. Meuh. C'est un son. Quel nom ? La vache. Oui. Le nom du son, c'est la vache. Un autre son, plus vif. Cot cot. Encore un son. Quel nom ? La poule. Oui. Le nom du son, c'est la poule. Près de l'auge, l'eau cloche. Un son. Quel nom ? L'eau. Oui. On entend un son. On dit le nom. Victorina répète, tout bas. Son. Nom. La vache, la poule, l'eau. Tu as nommé le son. Bravo, Victorina. Maman pose le panier. Dedans, des œufs. On compte des objets ? Un. Deux. Trois. Trois œufs. Tu as dit le nombre. Et tu as nommé les sons. Tu as fini d'écouter l'eau ? Encore un peu. D'accord.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zoé marche à la ferme avec papa. Un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt; arrive : meuh. Papa dit : c'est un son. Quel nom ? Zoé dit : la vache. Un autre son : cot cot. Zoé dit le nom : la poule. Près de l'auge, l'eau cloche. Zoé dit : l'eau. Papa dit : on entend un son. On dit le nom. Zoé répète : son, nom. La vache, la poule, l'eau.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La paille sent le soleil. Un grain de poussière danse dans un rayon. La barrière de bois est chaude. La terre est un peu collante sous les bottes. Un seau métallique attend près de l'auge. Une plume blanche est coincée dans le grillage. Le coq s'est tu, plus loin. La ferme est calme, ce matin, Victorina. Tu sens la paille ? Oui, papa. Ça pique un peu. J'arrive avec le panier. Je vous rejoins. En ce moment, Victorina marche près de papa. Un son arrive, grave. Meuh. C'est un son. Quel nom ? La vache. Oui. Le nom du son, c'est la vache. Un autre son, plus vif. Cot cot. Encore un son. Quel nom ? La poule. Oui. Le nom du son, c'est la poule. Près de l'auge, l'eau cloche. Un son. Quel nom ? L'eau. Oui. On entend un son. On dit le nom. Victorina répète, tout bas. Son. Nom. La vache, la poule, l'eau. Tu as nommé le son. Bravo, Victorina. Maman pose le panier. Dedans, des œufs. On compte des objets ? Un. Deux. Trois. Trois œufs. Tu as dit le nombre. Et tu as nommé les sons. Tu as fini d'écouter l'eau ? Encore un peu. D'accord.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1374,13 +1374,11 @@
 enfant-f|Trois œufs.
 papa|Tu as dit le nombre.
 papa|Et tu as nommé les sons.
-papa|C'est du bon travail.
 papa|Tu as fini d'écouter l'eau ?
 enfant-f|Encore un peu.
 maman|D'accord.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1410,7 +1408,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zoé entend un bruit. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1565,7 +1563,6 @@
 narrateur|C'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1590,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a entendu un son. Elle a dit le nom. Vache. Poule. Eau. Bravo. Tu as nommé le son. C'est du bon travail, Victorina. L'eau cloche encore. Oui. On dit le nom.</t>
+          <t>Victorina a entendu un son. Elle a dit le nom. Vache. Poule. Eau. Bravo. Tu as nommé le son. L'eau cloche encore. Oui. On dit le nom.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zoé a entendu un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt;. Elle a dit le nom. Vache. Poule. Eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a entendu un son. Elle a dit le nom. Vache. Poule. Eau. Bravo. Tu as nommé le son. L'eau cloche encore. Oui. On dit le nom.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1741,13 +1738,11 @@
 papa|Eau.
 papa|Bravo.
 maman|Tu as nommé le son.
-maman|C'est du bon travail, Victorina.
 enfant-f|L'eau cloche encore.
 papa|Oui.
 papa|On dit le nom.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1777,7 +1772,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;. Zoé écoute encore l'eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa donne la main. La main est chaude, un peu rêche. On écoute encore l'eau ? Oui, papa. Victorina écoute l'auge. L'eau cloche, tout doucement. Le panier est prêt. On rentre après, d'accord ? D'accord, maman. Tu as nommé le son.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1924,7 +1919,6 @@
 papa|Tu as nommé le son.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,12 +1943,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Victorina. Tu as fait du bon travail. La paille reste chaude dans le rayon. L'histoire est finie.</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Victorina. La paille reste chaude dans le rayon.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Victorina. La paille reste chaude dans le rayon.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2092,12 +2086,9 @@
           <t>enfant-f|J'ai entendu un son.
 enfant-f|J'ai dit le nom.
 papa|Bravo, Victorina.
-maman|Tu as fait du bon travail.
-narrateur|La paille reste chaude dans le rayon.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La paille reste chaude dans le rayon.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2116,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2161,6 +2152,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-02.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zoé, papa</t>
+          <t>Victorina, papa, maman</t>
         </is>
       </c>
     </row>
